--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/INDIANA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/INDIANA_2023.xlsx
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C164">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C316">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C907">
